--- a/untranslated/downloads/data-excel/16.4.2.1.xlsx
+++ b/untranslated/downloads/data-excel/16.4.2.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EB7DCF-17FD-4E6A-85CC-90443EEF7B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -67,8 +68,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +106,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -168,10 +176,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -179,6 +184,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -198,9 +206,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -238,9 +246,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -275,7 +283,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -310,7 +318,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -483,8 +491,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="35.85546875" style="1" customWidth="1"/>
@@ -492,7 +500,7 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -503,18 +511,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -526,8 +534,9 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
+      <c r="L3" s="11"/>
     </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -561,8 +570,11 @@
       <c r="K4" s="4">
         <v>2023</v>
       </c>
+      <c r="L4" s="4">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
@@ -590,14 +602,17 @@
       <c r="I5" s="1">
         <v>149</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="9" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="1">
         <v>219</v>
       </c>
+      <c r="L5" s="1">
+        <v>303</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -625,11 +640,14 @@
       <c r="I6" s="5">
         <v>159</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>15</v>
       </c>
       <c r="K6" s="5">
         <v>171</v>
+      </c>
+      <c r="L6" s="5">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
